--- a/study_case_model/scenario_variables/other_experiment_data/price_scenarios182.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/price_scenarios182.xlsx
@@ -451,7 +451,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>34.98021890511983</v>
+        <v>26.60788483330497</v>
       </c>
     </row>
     <row r="3">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.34383327265568</v>
+        <v>28.87789958732651</v>
       </c>
     </row>
     <row r="4">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.40483018874866</v>
+        <v>27.64789558884407</v>
       </c>
     </row>
     <row r="5">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.141423544527</v>
+        <v>27.08437982300321</v>
       </c>
     </row>
     <row r="6">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.35374921149424</v>
+        <v>31.97719605820404</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>25.92185683095282</v>
+        <v>31.03781355153157</v>
       </c>
     </row>
     <row r="8">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>34.95368187215476</v>
+        <v>25.95982956141619</v>
       </c>
     </row>
     <row r="9">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>28.66321495554934</v>
+        <v>28.65687508115493</v>
       </c>
     </row>
     <row r="10">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>28.56525431245456</v>
+        <v>27.66662487263251</v>
       </c>
     </row>
     <row r="11">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>28.36668391565756</v>
+        <v>26.61224280913847</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>31.55973306771507</v>
+        <v>31.30493352784022</v>
       </c>
     </row>
     <row r="13">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.46416012475536</v>
+        <v>31.14256815312644</v>
       </c>
     </row>
     <row r="14">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>28.33489094477354</v>
+        <v>27.27036044546937</v>
       </c>
     </row>
     <row r="15">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30.44122648458855</v>
+        <v>27.49939746991337</v>
       </c>
     </row>
     <row r="16">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>35.45760938955437</v>
+        <v>22.75949703656365</v>
       </c>
     </row>
     <row r="17">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>24.20997342710349</v>
+        <v>23.07776445586681</v>
       </c>
     </row>
     <row r="18">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.87235944075152</v>
+        <v>31.89778170005618</v>
       </c>
     </row>
     <row r="19">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21.3158594396549</v>
+        <v>25.86680024266881</v>
       </c>
     </row>
     <row r="20">
@@ -739,7 +739,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.7101531535759</v>
+        <v>28.09735042859205</v>
       </c>
     </row>
     <row r="21">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>30.92358931116819</v>
+        <v>27.86672975033057</v>
       </c>
     </row>
     <row r="22">
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.97313752787286</v>
+        <v>23.01382697094664</v>
       </c>
     </row>
     <row r="23">
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>24.15061491205131</v>
+        <v>22.8602656585226</v>
       </c>
     </row>
     <row r="24">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.73705426562465</v>
+        <v>32.0748953754258</v>
       </c>
     </row>
     <row r="25">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21.7089560638687</v>
+        <v>26.11949345094632</v>
       </c>
     </row>
     <row r="26">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.94343065674139</v>
+        <v>29.24557682852187</v>
       </c>
     </row>
     <row r="27">
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>26.01297690691823</v>
+        <v>24.93782460308122</v>
       </c>
     </row>
     <row r="28">
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>20.12959431011904</v>
+        <v>25.07411139238618</v>
       </c>
     </row>
     <row r="29">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.9593630219785</v>
+        <v>31.55658523921122</v>
       </c>
     </row>
     <row r="30">
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35.21026530381298</v>
+        <v>29.72507466336139</v>
       </c>
     </row>
     <row r="31">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>28.45790703355823</v>
+        <v>26.35780555230432</v>
       </c>
     </row>
     <row r="32">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>33.95829453372026</v>
+        <v>28.99864636405932</v>
       </c>
     </row>
     <row r="33">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>26.40373735698553</v>
+        <v>25.23623237706617</v>
       </c>
     </row>
     <row r="34">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>20.38220326967311</v>
+        <v>25.35099904734243</v>
       </c>
     </row>
     <row r="35">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>30.01921055818349</v>
+        <v>30.41767802826464</v>
       </c>
     </row>
     <row r="36">
@@ -995,7 +995,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>35.10077144207266</v>
+        <v>29.56361276820382</v>
       </c>
     </row>
     <row r="37">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>29.03644039197654</v>
+        <v>26.13636150265614</v>
       </c>
     </row>
     <row r="38">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>29.36069970944736</v>
+        <v>29.38742369756729</v>
       </c>
     </row>
     <row r="39">
@@ -1043,7 +1043,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>29.33706046615182</v>
+        <v>24.78267245465533</v>
       </c>
     </row>
     <row r="40">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>31.96979227822062</v>
+        <v>27.98045416652869</v>
       </c>
     </row>
     <row r="41">
@@ -1075,7 +1075,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>25.20031216688102</v>
+        <v>24.62385049571818</v>
       </c>
     </row>
     <row r="42">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>29.56261016633983</v>
+        <v>26.80708045710099</v>
       </c>
     </row>
     <row r="43">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>24.51131676762482</v>
+        <v>21.83092301903831</v>
       </c>
     </row>
     <row r="44">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>29.93638779853883</v>
+        <v>29.28675668812707</v>
       </c>
     </row>
     <row r="45">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>29.09561117135462</v>
+        <v>25.00495075846055</v>
       </c>
     </row>
     <row r="46">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>31.28632584171535</v>
+        <v>28.05627588112534</v>
       </c>
     </row>
     <row r="47">
@@ -1171,7 +1171,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>25.79650507906726</v>
+        <v>24.45555841831931</v>
       </c>
     </row>
     <row r="48">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>30.01555212232551</v>
+        <v>26.71177927628674</v>
       </c>
     </row>
     <row r="49">
@@ -1203,7 +1203,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>23.95225798354346</v>
+        <v>22.25849722136099</v>
       </c>
     </row>
     <row r="50">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>25.30482991117827</v>
+        <v>28.60618037122127</v>
       </c>
     </row>
     <row r="51">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>27.14155002038968</v>
+        <v>27.05013315218087</v>
       </c>
     </row>
     <row r="52">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>30.51093512499763</v>
+        <v>26.37847327731032</v>
       </c>
     </row>
     <row r="53">
@@ -1267,7 +1267,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>29.49800198242136</v>
+        <v>25.50282429417505</v>
       </c>
     </row>
     <row r="54">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>32.14984993054551</v>
+        <v>33.08898070689365</v>
       </c>
     </row>
     <row r="55">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>26.38256267761031</v>
+        <v>29.29124073127768</v>
       </c>
     </row>
     <row r="56">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>25.07155010653005</v>
+        <v>28.65243742977977</v>
       </c>
     </row>
     <row r="57">
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>26.96575453486847</v>
+        <v>26.88010858691476</v>
       </c>
     </row>
     <row r="58">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>30.33928433214779</v>
+        <v>25.9395178885796</v>
       </c>
     </row>
     <row r="59">
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>29.50487466433971</v>
+        <v>25.67163675700509</v>
       </c>
     </row>
     <row r="60">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>31.56295551377969</v>
+        <v>33.10806476252963</v>
       </c>
     </row>
     <row r="61">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>26.08881416824216</v>
+        <v>29.21928807998324</v>
       </c>
     </row>
     <row r="62">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>30.36075120461117</v>
+        <v>28.09684878099849</v>
       </c>
     </row>
     <row r="63">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25.98956833032423</v>
+        <v>27.05996198613889</v>
       </c>
     </row>
     <row r="64">
@@ -1443,7 +1443,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>25.10435936361054</v>
+        <v>23.58347322477558</v>
       </c>
     </row>
     <row r="65">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>28.87655689912872</v>
+        <v>27.39944721345274</v>
       </c>
     </row>
     <row r="66">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>30.5809818810386</v>
+        <v>25.84460746288654</v>
       </c>
     </row>
     <row r="67">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>26.93436228268546</v>
+        <v>21.9696413250683</v>
       </c>
     </row>
     <row r="68">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>30.66920012871208</v>
+        <v>28.85278849150201</v>
       </c>
     </row>
     <row r="69">
@@ -1523,7 +1523,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>25.92193830647283</v>
+        <v>26.72843518889447</v>
       </c>
     </row>
     <row r="70">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>24.89212514073051</v>
+        <v>24.05752351749882</v>
       </c>
     </row>
     <row r="71">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>27.96284630362478</v>
+        <v>27.08210362584027</v>
       </c>
     </row>
     <row r="72">
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>30.56526497457687</v>
+        <v>25.98090435146986</v>
       </c>
     </row>
     <row r="73">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>27.24064281510795</v>
+        <v>21.86523645568083</v>
       </c>
     </row>
     <row r="74">
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28.73816637407096</v>
+        <v>31.33680940623874</v>
       </c>
     </row>
     <row r="75">
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>27.14995174523761</v>
+        <v>28.47787908008164</v>
       </c>
     </row>
     <row r="76">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>38.37057918524157</v>
+        <v>32.25233920662741</v>
       </c>
     </row>
     <row r="77">
@@ -1651,7 +1651,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>30.64002244532553</v>
+        <v>27.29040828062853</v>
       </c>
     </row>
     <row r="78">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>31.26595392386372</v>
+        <v>28.74064320333913</v>
       </c>
     </row>
     <row r="79">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25.26251209597237</v>
+        <v>24.62005108844799</v>
       </c>
     </row>
     <row r="80">
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>28.68830359069904</v>
+        <v>31.22456456004716</v>
       </c>
     </row>
     <row r="81">
@@ -1715,7 +1715,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>26.96092631557367</v>
+        <v>29.1004221258021</v>
       </c>
     </row>
     <row r="82">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>38.21248167189698</v>
+        <v>32.79768696447722</v>
       </c>
     </row>
     <row r="83">
@@ -1747,7 +1747,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>30.56382995605217</v>
+        <v>27.43755011843408</v>
       </c>
     </row>
     <row r="84">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>31.39082607266072</v>
+        <v>28.81593646997632</v>
       </c>
     </row>
     <row r="85">
@@ -1779,7 +1779,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>25.15759773429223</v>
+        <v>23.89038809804828</v>
       </c>
     </row>
     <row r="86">
@@ -1795,7 +1795,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>27.79692181773999</v>
+        <v>28.23786302388999</v>
       </c>
     </row>
     <row r="87">
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>28.00480285187596</v>
+        <v>26.11937721934097</v>
       </c>
     </row>
     <row r="88">
@@ -1827,7 +1827,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>27.21400336805167</v>
+        <v>26.79213168755876</v>
       </c>
     </row>
     <row r="89">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>22.58723208769727</v>
+        <v>27.92527993032063</v>
       </c>
     </row>
     <row r="90">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>25.51531155078395</v>
+        <v>28.87864106129885</v>
       </c>
     </row>
     <row r="91">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>23.19488131412545</v>
+        <v>30.52827601234176</v>
       </c>
     </row>
     <row r="92">
@@ -1891,7 +1891,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>27.39200618968422</v>
+        <v>28.20589809757278</v>
       </c>
     </row>
     <row r="93">
@@ -1907,7 +1907,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>27.72656555908059</v>
+        <v>26.20912946593212</v>
       </c>
     </row>
     <row r="94">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>27.28219304133591</v>
+        <v>26.9601561785049</v>
       </c>
     </row>
     <row r="95">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>22.45172081413823</v>
+        <v>28.26248577909631</v>
       </c>
     </row>
     <row r="96">
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>25.19500966272757</v>
+        <v>28.93496090631277</v>
       </c>
     </row>
     <row r="97">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>23.37363104740045</v>
+        <v>30.78808629717381</v>
       </c>
     </row>
   </sheetData>
